--- a/TESTS/zlit_7_shiller_mitskevych.xlsx
+++ b/TESTS/zlit_7_shiller_mitskevych.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Фрідріх Шиллер — видатний німецький поет і драматург доби класицизму і романтизму</t>
+          <t>Фрідріх Шиллер</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Класицизм і романтизм — Шиллер разом з Гете є центральними фігурами «веймарського класицизму»</t>
+          <t>Класицизм і романтизм</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -687,6 +702,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -729,6 +749,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Бо він зрозумів що вона жорстоко грала його почуттями заради розваги — його гідність вища за будь-яке кохання</t>
+          <t>Бо він зрозумів що вона жорстоко грала його почуттями заради розваги</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Справжня гідність не терпить приниження — ніяке кохання не вимагає жертвувати власною честю і самоповагою</t>
+          <t>Справжня гідність не терпить приниження</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Польський поет-романтик XIX ст. — національний поет Польщі символ боротьби за незалежність</t>
+          <t>Польський поет-романтик XIX ст</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Поема про іспанського мавра Альманзора що вмираючи мстить ворогові — образ незламної гордості</t>
+          <t>Поема про іспанського мавра Альманзора що вмираючи мстить ворогові</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Незламний дух переможеного народу — поразка тіла не означає поразки духу; помста як останній акт гідності</t>
+          <t>Незламний дух переможеного народу</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Де відбувається сцена у баладі Шиллера «Рукавичка»?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>На турнірі</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>На публічному видовищі, де король і двір спостерігають, як леви і тигри б'ються між собою в ямі</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>На полюванні</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>При дворі в залі</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Як Кунігунда (дама) пояснила, чому кинула рукавичку в яму?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вона посперечалась з подругою</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона навмисне кинула рукавичку між хижаків, щоб перевірити силу кохання Делоржа</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона випадково впустила</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Хтось її штовхнув</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Як відреагував натовп, коли Делорж пішов до ями з хижаками?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Засміявся</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Завмер у напруженому очікуванні — усі розуміли смертельну небезпеку</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Захлопав одразу</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Розійшовся</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Чим Делорж здивував і дружину, і глядачів після повернення з ями?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Попросив нагороди</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Кинув рукавичку прямо в обличчя дамі і публічно відмовився від неї</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Оголосив вірність назавжди</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Поклав рукавичку до ніг короля</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Що його вчинок говорить про розуміння Делоржем кохання і гідності?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Що кохання все вибачає</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Що справжня гідність не потерпить маніпуляцій і публічного приниження заради гри</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Що він не любить даму</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Що він боягуз</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Яку роль у баладі відіграють хижаки у ямі?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Символ зла</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Інструмент жорстокого випробування — вони реальна смертельна небезпека, а не декорація</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Алегорія пристрастей</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Прикраса для видовища</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Яке значення має Вестерплятте у балади Шиллера «Рукавичка»?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Велике</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Жодного — це різні твори, зміст не перетинається</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вестерплятте згадано в баладі</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>Лише символічне</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>Г</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Чим балада як жанр відрізняється від ліричного вірша?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічим суттєвим</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Балада має чіткий розповідний сюжет з дійовими особами, конфліктом і розв'язкою</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Балада — це проза</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Балада завжди коротша</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Яка риторична сила балади як жанру порівняно з есеєм на ту ж тему?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Есей завжди переконливіший</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Балада діє через конкретну напружену сцену і образи — читач переживає, а не лише розуміє</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Риторичної сили немає</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони однакові</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Яку тему розкриває балада «Альпухара» Міцкевича?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Красу Альпухари</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Незламний дух переможеного іспанського мавра Альманзора, що мститься загарбникам перед смертю</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Любовна трагедія</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Природні явища в Іспанії</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Що зробив Альманзор, умираючи від рани серед переможців?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Попросив пощади</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вдав, що готовий хрестити народ і кинув у зібраних смертоносну заразу — остання помста</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Почав молитись</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Здався і підписав мир</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Яку ідею несе вчинок Альманзора у баладі «Альпухара»?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Що помста виправдовує будь-які засоби</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Що дух завойованого народу не зламаний, навіть коли тіло вже знищене</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Що іспанські маври були злочинцями</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Що зрада морально виправдана</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Де знаходиться озеро Світязь і що з ним пов'язане?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В Альпах</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У Литві/Польщі — за легендою, під водою озера схований затоплений город</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>В Іспанії</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>В Україні</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Що сталося з містом і його мешканцями, за переказом балади «Світязь»?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Місто спалили вороги</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Місто опустилось під воду разом з жителями — і дівчата стали квітами-русалками</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Місто покинули добровільно</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Місто знесли за наказом короля</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Про що молились дівчата, не бажаючи потрапити до рук ворогів?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Про чудо перемоги</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Про перетворення на що завгодно, аби лише уникнути полону і ганьби</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Про дощ і захист</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Про смерть ворогів</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Яку спільну ідею несуть «Альпухара» і «Світязь» разом?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Що поразка завжди ганебна</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Що є цінності дорожчі за саме фізичне виживання — гідність і честь переможеного народу</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Що помста — завжди добро</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Що природа важливіша за людей</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Яке значення має творчість Міцкевича для польської національної ідентичності?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лише літературне</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він є символом польського духу і спротиву в добу поділів Польщі між загарбниками</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Жодного особливого</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише регіональне</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Що спільного між баладами Шиллера і Міцкевича щодо центральної теми?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Обидва лише про кохання</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Обидва стверджують: гідність і честь людини важливіші за страх, зручність чи фізичне виживання</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Обидва про природу</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Обидва про середньовічні битви</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Яку роль відіграє романтизм у баладах Шиллера і Міцкевича?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Романтизм лише прикраса</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Романтизм надає героїчним вчинкам піднесеного виміру, оспівуючи вільний дух і моральний вибір</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Романтизм не присутній у баладах</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Романтизм означає лише любовну тематику</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Чим балада «Рукавичка» цікава учням 7 класу в контексті стосунків і поваги?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічим особливим для підлітків</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона показує, що справжня повага і кохання несумісні з маніпуляцією і публічним приниженням</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона про тварин і нічого більше</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона суто для дорослих</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Яку мораль можна сформулювати, узагальнивши всі чотири твори у темі (Шиллер, Міцкевич ×3)?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сила і перемога — найголовніше</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Гідність людини проявляється в моменті найважчого вибору — і ця гідність важливіша за власну вигоду чи виживання</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Поразка завжди ганебна</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Природа завжди перемагає людину</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Яку національну ідею виражає творчість Міцкевича?</t>
+          <t>Балади Шиллера і Міцкевича об'єднує тема гідності й честі — людської та народної — перед обличчям тиску, небезпеки чи поразки.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,29 +2133,32 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Що символізує озеро Світязь у баладі Міцкевича?</t>
+          <t>Символ озера Світязь у баладі Міцкевича — краса природи і більше нічого.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яку риторичну силу мають балади як жанр?</t>
+          <t>Балада як жанр у романтичній традиції поєднує ліричний пафос з чітким розповідним сюжетом і пристрастями героїв.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Що спільного між баладами Шиллера і Міцкевича?</t>
+          <t>«Рукавичка» і «Альпухара» мають спільну тему: гідність не терпить зради власних цінностей — навіть заради кохання чи порятунку.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яку роль відіграє романтизм у баладах Шиллера і Міцкевича?</t>
+          <t>Романтизм у баладах Шиллера і Міцкевича надає героїчним вчинкам піднесеного виміру і стверджує свободу духу над обставинами.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Що таке «балада» як жанр у романтичній традиції?</t>
+          <t>«Балада» як жанр — це лише пісня з приспівом, без сюжету і без морального виміру.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які теми об'єднують балади Шиллера і Міцкевича?</t>
+          <t>Що об'єднує чотири твори у темі Шиллера і Міцкевича?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Гідність і честь</t>
+          <t>Делорж відмовився від дами заради гідності</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Боротьба духу над обставинами</t>
+          <t>Альманзор зберіг дух народу перед смертю</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Любов до природи</t>
+          <t>Всі герої обрали легкий шлях уникнення конфлікту</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Незламність перед лицем поразки</t>
+          <t>Дівчата Світязі обрали перетворення замість ганебного полону</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Легенду про озеро де затонуло місто — дівчата перетворились на русалок щоб не потрапити в полон до ворогів</t>
+          <t>Легенду про озеро де затонуло місто</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Щоб не потрапити в ганебний полон до ворогів — смерть і перетворення кращі за безчестя</t>
+          <t>Щоб не потрапити в ганебний полон до ворогів</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Гідність перед лицем поразки — люди обирають смерть або помсту а не ганебну капітуляцію</t>
+          <t>Гідність перед лицем поразки</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
